--- a/data/hydroExample/Power_Parameters.xlsx
+++ b/data/hydroExample/Power_Parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo2\data\hydroExample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A1DDC6-6110-4A49-B21A-F7A68F2FC4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612D4FD1-94F3-4189-9A74-5DCB670E6972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" tabRatio="958" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,6 +445,7 @@
       <i/>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1309,7 +1310,7 @@
         <v>73</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>74</v>
@@ -1332,7 +1333,7 @@
         <v>76</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>77</v>
@@ -1378,7 +1379,7 @@
         <v>79</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>80</v>
@@ -1933,18 +1934,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2094,14 +2095,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13778B2C-CE05-4B32-8196-2F381FEAC95A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0155F7A0-74CD-4575-8C0B-A34C113F80FE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -2113,6 +2106,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13778B2C-CE05-4B32-8196-2F381FEAC95A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/hydroExample/Power_Parameters.xlsx
+++ b/data/hydroExample/Power_Parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo2\data\hydroExample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612D4FD1-94F3-4189-9A74-5DCB670E6972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D0E89E-136E-4A0C-9464-9AC60E82AD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" tabRatio="958" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1426,7 +1426,7 @@
         <v>29</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>30</v>
@@ -1505,7 +1505,7 @@
         <v>66</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1934,21 +1934,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004934E3CB1C58BA43BC6E229E2BF20201" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e33ccc94e63df24f58cb47229b46e190">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87003a75-b64f-4b22-bf19-aa30740e3d46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f0f7a5bb162b669de9ce8ff8278c29f" ns2:_="">
     <xsd:import namespace="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
@@ -2094,7 +2079,40 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{773946F7-566C-458F-95C9-79B0CCE20E87}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0155F7A0-74CD-4575-8C0B-A34C113F80FE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -2110,28 +2128,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13778B2C-CE05-4B32-8196-2F381FEAC95A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{773946F7-566C-458F-95C9-79B0CCE20E87}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>